--- a/Assets/Data/Commodore/C64/KU-14194HB/Data C64 KU-14194HB v2.0.0.xlsx
+++ b/Assets/Data/Commodore/C64/KU-14194HB/Data C64 KU-14194HB v2.0.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dennis\AppData\Local\Classic-Repair-Toolbox\Data\Commodore\C64\KU-14194HB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.10\all\mydir\http\classic-repair-toolbox.dk\public_html\app-data\Data\Commodore\C64\KU-14194HB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E6FC73-6AD2-4CCF-A865-426089556DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686520B9-1055-495C-85A7-15018742BF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3348" uniqueCount="1329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3352" uniqueCount="1332">
   <si>
     <r>
       <t xml:space="preserve"># Hardware: </t>
@@ -4088,6 +4088,24 @@
     <t>Commodore/Shared files/Board local files/Commodore 64-128 Best-Practises.txt</t>
   </si>
   <si>
+    <t>Forum64; Repair Corner (primarily German)</t>
+  </si>
+  <si>
+    <t>https://www.forum64.de/index.php?board/183-repair-corner/</t>
+  </si>
+  <si>
+    <t>d173a473-e678-4918-87df-35bbf6ed7113</t>
+  </si>
+  <si>
+    <t>Zimmers; Character ROMs</t>
+  </si>
+  <si>
+    <t>https://www.zimmers.net/anonftp/pub/cbm/firmware/characters/</t>
+  </si>
+  <si>
+    <t>cfab6b79-6647-456d-afd8-9806eb4d2a50</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve"># Revision date: </t>
     </r>
@@ -4099,17 +4117,8 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2026-May-12</t>
+      <t>2026-June-24</t>
     </r>
-  </si>
-  <si>
-    <t>Forum64; Repair Corner (primarily German)</t>
-  </si>
-  <si>
-    <t>https://www.forum64.de/index.php?board/183-repair-corner/</t>
-  </si>
-  <si>
-    <t>d173a473-e678-4918-87df-35bbf6ed7113</t>
   </si>
 </sst>
 </file>
@@ -4737,7 +4746,7 @@
     </row>
     <row r="3" spans="1:9" s="11" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
       <c r="H3" s="38"/>
       <c r="I3"/>
@@ -8195,7 +8204,7 @@
         <v>385</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>321</v>
@@ -18425,7 +18434,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9014B11-7294-4050-ABF4-8B4EFBD7F103}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" customWidth="1"/>
@@ -18512,64 +18521,75 @@
     </row>
     <row r="11" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>731</v>
+        <v>1328</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>732</v>
+        <v>1329</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>733</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>731</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>732</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="34" t="s">
         <v>392</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B13" s="41" t="s">
         <v>734</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C13" s="41" t="s">
         <v>735</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="D13" s="41" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>392</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>1110</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>1111</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="D14" s="41" t="s">
         <v>1112</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="41" t="s">
+    <row r="15" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="41" t="s">
         <v>519</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B15" s="41" t="s">
         <v>1105</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C15" s="41" t="s">
         <v>1104</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D15" s="41" t="s">
         <v>1106</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="D16" s="31"/>
-    </row>
+    <row r="16" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D17" s="31"/>
     </row>
@@ -18579,28 +18599,28 @@
     <row r="19" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D19" s="31"/>
     </row>
-    <row r="20" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D20" s="31"/>
+    </row>
     <row r="21" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="34"/>
-    </row>
+    <row r="25" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="34"/>
     </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D33" s="36"/>
-    </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D35" s="36"/>
-    </row>
-    <row r="48" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D48" s="5"/>
-    </row>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D54" s="1"/>
+    <row r="27" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="34"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D34" s="36"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D36" s="36"/>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D49" s="5"/>
     </row>
     <row r="55" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D55" s="1"/>
@@ -18613,6 +18633,9 @@
     </row>
     <row r="58" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D58" s="1"/>
+    </row>
+    <row r="59" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D59" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19089,13 +19112,13 @@
         <v>794</v>
       </c>
       <c r="B23" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C23" t="s">
         <v>1326</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>1327</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">

--- a/Assets/Data/Commodore/C64/KU-14194HB/Data C64 KU-14194HB v2.0.0.xlsx
+++ b/Assets/Data/Commodore/C64/KU-14194HB/Data C64 KU-14194HB v2.0.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.20.10\all\mydir\http\classic-repair-toolbox.dk\public_html\app-data\Data\Commodore\C64\KU-14194HB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686520B9-1055-495C-85A7-15018742BF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDBFBAFF-D493-4CF0-9C12-F60196185DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Board schematics" sheetId="5" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3352" uniqueCount="1332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3352" uniqueCount="1335">
   <si>
     <r>
       <t xml:space="preserve"># Hardware: </t>
@@ -1953,9 +1953,6 @@
     <t>33Ω</t>
   </si>
   <si>
-    <t>Resistor pack, 8 pin</t>
-  </si>
-  <si>
     <t>0ae0b509-0ff5-4c47-b98f-c0b0e4a177f3</t>
   </si>
   <si>
@@ -1978,9 +1975,6 @@
   </si>
   <si>
     <t>3.3KΩ 1/4W</t>
-  </si>
-  <si>
-    <t>Resistor pack, 10 pin</t>
   </si>
   <si>
     <t>3e2132ba-d53c-4e3b-b0b4-35d2ca2fd40d</t>
@@ -3418,9 +3412,6 @@
     <t>6930f05a-7e30-4b02-9bff-65983990e026</t>
   </si>
   <si>
-    <t>Resistor packs must be mounted with GND pin at its designated position</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=oeoPu2S6TQg&amp;t=810s</t>
   </si>
   <si>
@@ -3900,12 +3891,6 @@
   </si>
   <si>
     <t>Generic shared files/Component images/resistor_330_5.png</t>
-  </si>
-  <si>
-    <t>Generic shared files/Component images/resistor_pack_8pin.png</t>
-  </si>
-  <si>
-    <t>Generic shared files/Component images/resistor_pack_10pin.png</t>
   </si>
   <si>
     <t>Generic shared files/Component images/2SC1815.png</t>
@@ -4117,8 +4102,34 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2026-June-24</t>
+      <t>2026-August-21</t>
     </r>
+  </si>
+  <si>
+    <t>Resistor pack, 8 pin, isolated</t>
+  </si>
+  <si>
+    <t>Resistor pack, 8 pin, bussed</t>
+  </si>
+  <si>
+    <t>Resistor pack, 10 pin, bussed</t>
+  </si>
+  <si>
+    <t>Generic shared files/Component images/resistor_pack_8pin_isolated.png</t>
+  </si>
+  <si>
+    <t>Generic shared files/Component images/resistor_pack_8pin_bussed.png</t>
+  </si>
+  <si>
+    <t>Generic shared files/Component images/resistor_pack_10pin_bussed.png</t>
+  </si>
+  <si>
+    <t>Resistor packs must be mounted with GND pin at its designated position.
+Note this resistor pack is isolated, and by then each two pin is its own pair (pin 1+2, pin 3+4 and pin 5+6 etc).</t>
+  </si>
+  <si>
+    <t>Resistor packs must be mounted with GND pin at its designated position.
+Note this resistor pack is bussed, and by then each pin share pin 1 as GROUND.</t>
   </si>
 </sst>
 </file>
@@ -4746,7 +4757,7 @@
     </row>
     <row r="3" spans="1:9" s="11" customFormat="1" ht="21" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="H3" s="38"/>
       <c r="I3"/>
@@ -4816,16 +4827,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="D9" s="33" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F9" s="33" t="s">
         <v>1196</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>1199</v>
       </c>
       <c r="G9" s="33" t="s">
         <v>8</v>
@@ -4842,7 +4853,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>12</v>
@@ -4851,7 +4862,7 @@
         <v>0.3</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>12</v>
@@ -4871,7 +4882,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>12</v>
@@ -4880,7 +4891,7 @@
         <v>0.3</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>12</v>
@@ -4900,7 +4911,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>12</v>
@@ -4909,7 +4920,7 @@
         <v>0.3</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>12</v>
@@ -9308,7 +9319,7 @@
         <v>35</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="H180" t="s">
         <v>523</v>
@@ -10270,15 +10281,15 @@
         <v>35</v>
       </c>
       <c r="G219" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="H219" t="s">
         <v>628</v>
-      </c>
-      <c r="H219" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>35</v>
@@ -10296,93 +10307,93 @@
         <v>35</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>628</v>
+        <v>1327</v>
       </c>
       <c r="H220" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C221" s="1" t="s">
         <v>632</v>
-      </c>
-      <c r="B221" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>633</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>542</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>628</v>
+        <v>1328</v>
       </c>
       <c r="H221" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C222" s="1" t="s">
         <v>635</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>636</v>
       </c>
       <c r="E222" s="1" t="s">
         <v>542</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>637</v>
+        <v>1329</v>
       </c>
       <c r="H222" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G223" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H223" t="s">
         <v>639</v>
-      </c>
-      <c r="B223" s="1" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>1093</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="F223" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G223" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H223" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B224" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D224" s="1" t="s">
         <v>1091</v>
       </c>
-      <c r="C224" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>1093</v>
-      </c>
       <c r="E224" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>35</v>
@@ -10391,24 +10402,24 @@
         <v>35</v>
       </c>
       <c r="H224" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B225" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D225" s="1" t="s">
         <v>1086</v>
       </c>
-      <c r="C225" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D225" s="1" t="s">
-        <v>1088</v>
-      </c>
       <c r="E225" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>35</v>
@@ -10417,24 +10428,24 @@
         <v>35</v>
       </c>
       <c r="H225" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B226" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D226" s="1" t="s">
         <v>1091</v>
       </c>
-      <c r="C226" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D226" s="1" t="s">
-        <v>1093</v>
-      </c>
       <c r="E226" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>35</v>
@@ -10443,30 +10454,30 @@
         <v>35</v>
       </c>
       <c r="H226" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B227" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D227" s="1" t="s">
         <v>1091</v>
       </c>
-      <c r="C227" s="1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D227" s="1" t="s">
-        <v>1093</v>
-      </c>
       <c r="E227" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>35</v>
       </c>
       <c r="H227" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
   </sheetData>
@@ -10531,7 +10542,7 @@
     </row>
     <row r="5" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="25"/>
@@ -10547,7 +10558,7 @@
     </row>
     <row r="7" spans="1:11" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="26"/>
@@ -10568,28 +10579,28 @@
         <v>28</v>
       </c>
       <c r="C8" s="44" t="s">
+        <v>650</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>652</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="F8" s="16" t="s">
         <v>653</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="G8" s="16" t="s">
         <v>654</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="H8" s="16" t="s">
         <v>655</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="I8" s="16" t="s">
         <v>656</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="J8" s="16" t="s">
         <v>657</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>658</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>659</v>
       </c>
       <c r="K8" s="45" t="s">
         <v>10</v>
@@ -10602,16 +10613,16 @@
       <c r="B9" s="14"/>
       <c r="C9" s="27"/>
       <c r="D9" s="5" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K9" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -10621,16 +10632,16 @@
       <c r="B10" s="14"/>
       <c r="C10" s="27"/>
       <c r="D10" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J10" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K10" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -10640,16 +10651,16 @@
       <c r="B11" s="14"/>
       <c r="C11" s="27"/>
       <c r="D11" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J11" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K11" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -10659,16 +10670,16 @@
       <c r="B12" s="14"/>
       <c r="C12" s="27"/>
       <c r="D12" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J12" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K12" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -10678,16 +10689,16 @@
       <c r="B13" s="14"/>
       <c r="C13" s="27"/>
       <c r="D13" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J13" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K13" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -10697,16 +10708,16 @@
       <c r="B14" s="14"/>
       <c r="C14" s="27"/>
       <c r="D14" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J14" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K14" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -10716,16 +10727,16 @@
       <c r="B15" s="14"/>
       <c r="C15" s="27"/>
       <c r="D15" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J15" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K15" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -10735,16 +10746,16 @@
       <c r="B16" s="14"/>
       <c r="C16" s="27"/>
       <c r="D16" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J16" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K16" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -10754,16 +10765,16 @@
       <c r="B17" s="14"/>
       <c r="C17" s="27"/>
       <c r="D17" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -10773,16 +10784,16 @@
       <c r="B18" s="14"/>
       <c r="C18" s="27"/>
       <c r="D18" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I18" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J18" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -10792,16 +10803,16 @@
       <c r="B19" s="14"/>
       <c r="C19" s="27"/>
       <c r="D19" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J19" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -10811,16 +10822,16 @@
       <c r="B20" s="14"/>
       <c r="C20" s="27"/>
       <c r="D20" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J20" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -10830,16 +10841,16 @@
       <c r="B21" s="14"/>
       <c r="C21" s="27"/>
       <c r="D21" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I21" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J21" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K21" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -10849,16 +10860,16 @@
       <c r="B22" s="14"/>
       <c r="C22" s="27"/>
       <c r="D22" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J22" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K22" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -10868,16 +10879,16 @@
       <c r="B23" s="14"/>
       <c r="C23" s="27"/>
       <c r="D23" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J23" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K23" s="36" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -10887,16 +10898,16 @@
       <c r="B24" s="14"/>
       <c r="C24" s="27"/>
       <c r="D24" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J24" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K24" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -10906,16 +10917,16 @@
       <c r="B25" s="14"/>
       <c r="C25" s="27"/>
       <c r="D25" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I25" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J25" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K25" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -10925,16 +10936,16 @@
       <c r="B26" s="14"/>
       <c r="C26" s="27"/>
       <c r="D26" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J26" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K26" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -10944,16 +10955,16 @@
       <c r="B27" s="14"/>
       <c r="C27" s="27"/>
       <c r="D27" s="12" t="s">
+        <v>659</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>1215</v>
+      </c>
+      <c r="J27" s="30" t="s">
         <v>661</v>
       </c>
-      <c r="I27" s="12" t="s">
-        <v>1218</v>
-      </c>
-      <c r="J27" s="30" t="s">
-        <v>663</v>
-      </c>
       <c r="K27" s="36" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -10963,16 +10974,16 @@
       <c r="B28" s="14"/>
       <c r="C28" s="27"/>
       <c r="D28" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="J28" s="30" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="K28" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -10982,16 +10993,16 @@
       <c r="B29" s="14"/>
       <c r="C29" s="27"/>
       <c r="D29" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="J29" s="30" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="K29" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11001,16 +11012,16 @@
       <c r="B30" s="14"/>
       <c r="C30" s="27"/>
       <c r="D30" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J30" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K30" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11020,16 +11031,16 @@
       <c r="B31" s="14"/>
       <c r="C31" s="27"/>
       <c r="D31" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J31" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K31" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -11039,16 +11050,16 @@
       <c r="B32" s="14"/>
       <c r="C32" s="27"/>
       <c r="D32" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J32" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K32" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11058,16 +11069,16 @@
       <c r="B33" s="14"/>
       <c r="C33" s="27"/>
       <c r="D33" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J33" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K33" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11077,16 +11088,16 @@
       <c r="B34" s="14"/>
       <c r="C34" s="27"/>
       <c r="D34" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J34" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K34" s="36" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11096,16 +11107,16 @@
       <c r="B35" s="14"/>
       <c r="C35" s="27"/>
       <c r="D35" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J35" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K35" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11115,16 +11126,16 @@
       <c r="B36" s="14"/>
       <c r="C36" s="27"/>
       <c r="D36" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J36" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K36" s="36" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11134,16 +11145,16 @@
       <c r="B37" s="14"/>
       <c r="C37" s="27"/>
       <c r="D37" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J37" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K37" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11153,16 +11164,16 @@
       <c r="B38" s="14"/>
       <c r="C38" s="27"/>
       <c r="D38" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J38" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K38" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11172,16 +11183,16 @@
       <c r="B39" s="14"/>
       <c r="C39" s="27"/>
       <c r="D39" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J39" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K39" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11191,16 +11202,16 @@
       <c r="B40" s="14"/>
       <c r="C40" s="27"/>
       <c r="D40" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J40" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K40" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11210,16 +11221,16 @@
       <c r="B41" s="14"/>
       <c r="C41" s="27"/>
       <c r="D41" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J41" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K41" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -11229,16 +11240,16 @@
       <c r="B42" s="14"/>
       <c r="C42" s="27"/>
       <c r="D42" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I42" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J42" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K42" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11248,16 +11259,16 @@
       <c r="B43" s="14"/>
       <c r="C43" s="27"/>
       <c r="D43" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I43" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J43" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K43" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11267,16 +11278,16 @@
       <c r="B44" s="14"/>
       <c r="C44" s="27"/>
       <c r="D44" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I44" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="K44" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11286,16 +11297,16 @@
       <c r="B45" s="14"/>
       <c r="C45" s="27"/>
       <c r="D45" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I45" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J45" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K45" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11305,16 +11316,16 @@
       <c r="B46" s="14"/>
       <c r="C46" s="27"/>
       <c r="D46" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J46" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K46" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11324,16 +11335,16 @@
       <c r="B47" s="14"/>
       <c r="C47" s="27"/>
       <c r="D47" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J47" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K47" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11343,16 +11354,16 @@
       <c r="B48" s="14"/>
       <c r="C48" s="27"/>
       <c r="D48" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I48" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J48" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11362,16 +11373,16 @@
       <c r="B49" s="14"/>
       <c r="C49" s="27"/>
       <c r="D49" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J49" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K49" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11381,16 +11392,16 @@
       <c r="B50" s="14"/>
       <c r="C50" s="27"/>
       <c r="D50" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J50" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K50" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11400,16 +11411,16 @@
       <c r="B51" s="14"/>
       <c r="C51" s="27"/>
       <c r="D51" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J51" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K51" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11419,16 +11430,16 @@
       <c r="B52" s="14"/>
       <c r="C52" s="27"/>
       <c r="D52" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I52" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J52" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K52" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11438,16 +11449,16 @@
       <c r="B53" s="14"/>
       <c r="C53" s="27"/>
       <c r="D53" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I53" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J53" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K53" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11457,16 +11468,16 @@
       <c r="B54" s="14"/>
       <c r="C54" s="27"/>
       <c r="D54" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J54" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11476,16 +11487,16 @@
       <c r="B55" s="14"/>
       <c r="C55" s="27"/>
       <c r="D55" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J55" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11495,16 +11506,16 @@
       <c r="B56" s="14"/>
       <c r="C56" s="27"/>
       <c r="D56" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J56" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11514,16 +11525,16 @@
       <c r="B57" s="14"/>
       <c r="C57" s="27"/>
       <c r="D57" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J57" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11533,16 +11544,16 @@
       <c r="B58" s="14"/>
       <c r="C58" s="27"/>
       <c r="D58" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I58" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J58" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11552,16 +11563,16 @@
       <c r="B59" s="14"/>
       <c r="C59" s="27"/>
       <c r="D59" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I59" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J59" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K59" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11571,16 +11582,16 @@
       <c r="B60" s="14"/>
       <c r="C60" s="27"/>
       <c r="D60" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J60" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K60" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11590,16 +11601,16 @@
       <c r="B61" s="14"/>
       <c r="C61" s="27"/>
       <c r="D61" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J61" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K61" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -11609,16 +11620,16 @@
       <c r="B62" s="14"/>
       <c r="C62" s="27"/>
       <c r="D62" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I62" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J62" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K62" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11628,16 +11639,16 @@
       <c r="B63" s="14"/>
       <c r="C63" s="27"/>
       <c r="D63" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J63" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K63" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11647,16 +11658,16 @@
       <c r="B64" s="14"/>
       <c r="C64" s="27"/>
       <c r="D64" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J64" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K64" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11666,16 +11677,16 @@
       <c r="B65" s="14"/>
       <c r="C65" s="27"/>
       <c r="D65" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I65" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J65" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K65" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -11685,16 +11696,16 @@
       <c r="B66" s="14"/>
       <c r="C66" s="27"/>
       <c r="D66" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J66" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K66" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11704,16 +11715,16 @@
       <c r="B67" s="14"/>
       <c r="C67" s="27"/>
       <c r="D67" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K67" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -11723,16 +11734,16 @@
       <c r="B68" s="14"/>
       <c r="C68" s="27"/>
       <c r="D68" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J68" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K68" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -11742,16 +11753,16 @@
       <c r="B69" s="14"/>
       <c r="C69" s="27"/>
       <c r="D69" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I69" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J69" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K69" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11761,16 +11772,16 @@
       <c r="B70" s="14"/>
       <c r="C70" s="27"/>
       <c r="D70" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J70" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K70" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11780,16 +11791,16 @@
       <c r="B71" s="14"/>
       <c r="C71" s="27"/>
       <c r="D71" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I71" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J71" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K71" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11799,16 +11810,16 @@
       <c r="B72" s="14"/>
       <c r="C72" s="27"/>
       <c r="D72" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J72" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K72" s="36" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11818,16 +11829,16 @@
       <c r="B73" s="14"/>
       <c r="C73" s="27"/>
       <c r="D73" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J73" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K73" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11839,16 +11850,16 @@
       </c>
       <c r="C74" s="27"/>
       <c r="D74" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I74" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J74" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K74" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11860,16 +11871,16 @@
       </c>
       <c r="C75" s="27"/>
       <c r="D75" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I75" s="12" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="J75" s="30" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="K75" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11879,16 +11890,16 @@
       <c r="B76" s="14"/>
       <c r="C76" s="27"/>
       <c r="D76" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I76" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J76" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K76" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11898,16 +11909,16 @@
       <c r="B77" s="14"/>
       <c r="C77" s="27"/>
       <c r="D77" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I77" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J77" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K77" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11917,16 +11928,16 @@
       <c r="B78" s="14"/>
       <c r="C78" s="27"/>
       <c r="D78" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I78" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J78" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K78" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11936,16 +11947,16 @@
       <c r="B79" s="14"/>
       <c r="C79" s="27"/>
       <c r="D79" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I79" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J79" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K79" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11955,16 +11966,16 @@
       <c r="B80" s="14"/>
       <c r="C80" s="27"/>
       <c r="D80" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I80" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J80" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K80" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -11974,16 +11985,16 @@
       <c r="B81" s="14"/>
       <c r="C81" s="27"/>
       <c r="D81" s="12" t="s">
+        <v>659</v>
+      </c>
+      <c r="I81" s="12" t="s">
+        <v>1215</v>
+      </c>
+      <c r="J81" s="30" t="s">
         <v>661</v>
       </c>
-      <c r="I81" s="12" t="s">
-        <v>1218</v>
-      </c>
-      <c r="J81" s="30" t="s">
-        <v>663</v>
-      </c>
       <c r="K81" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -11993,16 +12004,16 @@
       <c r="B82" s="14"/>
       <c r="C82" s="27"/>
       <c r="D82" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I82" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J82" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K82" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -12012,16 +12023,16 @@
       <c r="B83" s="14"/>
       <c r="C83" s="27"/>
       <c r="D83" s="12" t="s">
+        <v>659</v>
+      </c>
+      <c r="I83" s="12" t="s">
+        <v>1215</v>
+      </c>
+      <c r="J83" s="30" t="s">
         <v>661</v>
       </c>
-      <c r="I83" s="12" t="s">
-        <v>1218</v>
-      </c>
-      <c r="J83" s="30" t="s">
-        <v>663</v>
-      </c>
       <c r="K83" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -12031,16 +12042,16 @@
       <c r="B84" s="14"/>
       <c r="C84" s="27"/>
       <c r="D84" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I84" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J84" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K84" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -12050,16 +12061,16 @@
       <c r="B85" s="14"/>
       <c r="C85" s="27"/>
       <c r="D85" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I85" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J85" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K85" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -12069,16 +12080,16 @@
       <c r="B86" s="14"/>
       <c r="C86" s="27"/>
       <c r="D86" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I86" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J86" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K86" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -12088,16 +12099,16 @@
       <c r="B87" s="14"/>
       <c r="C87" s="27"/>
       <c r="D87" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I87" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J87" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K87" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -12107,16 +12118,16 @@
       <c r="B88" s="14"/>
       <c r="C88" s="27"/>
       <c r="D88" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I88" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J88" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K88" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -12126,16 +12137,16 @@
       <c r="B89" s="14"/>
       <c r="C89" s="27"/>
       <c r="D89" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I89" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J89" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K89" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -12145,16 +12156,16 @@
       <c r="B90" s="14"/>
       <c r="C90" s="27"/>
       <c r="D90" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I90" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J90" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K90" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -12164,16 +12175,16 @@
       <c r="B91" s="14"/>
       <c r="C91" s="27"/>
       <c r="D91" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I91" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J91" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K91" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -12183,16 +12194,16 @@
       <c r="B92" s="14"/>
       <c r="C92" s="27"/>
       <c r="D92" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I92" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J92" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K92" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -12202,16 +12213,16 @@
       <c r="B93" s="14"/>
       <c r="C93" s="27"/>
       <c r="D93" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I93" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J93" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K93" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -12221,16 +12232,16 @@
       <c r="B94" s="14"/>
       <c r="C94" s="27"/>
       <c r="D94" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I94" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J94" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K94" s="36" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -12240,16 +12251,16 @@
       <c r="B95" s="14"/>
       <c r="C95" s="27"/>
       <c r="D95" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I95" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J95" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K95" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -12259,16 +12270,16 @@
       <c r="B96" s="14"/>
       <c r="C96" s="27"/>
       <c r="D96" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I96" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J96" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K96" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="97" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -12278,16 +12289,16 @@
       <c r="B97" s="14"/>
       <c r="C97" s="27"/>
       <c r="D97" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I97" s="12" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="J97" s="30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="K97" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="72" x14ac:dyDescent="0.3">
@@ -12297,16 +12308,16 @@
       <c r="B98" s="14"/>
       <c r="C98" s="27"/>
       <c r="D98" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I98" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J98" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K98" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="72" x14ac:dyDescent="0.3">
@@ -12316,16 +12327,16 @@
       <c r="B99" s="14"/>
       <c r="C99" s="27"/>
       <c r="D99" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I99" s="12" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="J99" s="30" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="K99" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.3">
@@ -12335,16 +12346,16 @@
       <c r="B100" s="14"/>
       <c r="C100" s="27"/>
       <c r="D100" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I100" s="12" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="J100" s="30" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="K100" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.3">
@@ -12354,14 +12365,14 @@
       <c r="B101" s="14"/>
       <c r="C101" s="27"/>
       <c r="D101" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I101" s="12" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="J101" s="30"/>
       <c r="K101" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="102" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
@@ -12371,16 +12382,16 @@
       <c r="B102" s="14"/>
       <c r="C102" s="27"/>
       <c r="D102" s="52" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="I102" s="12" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="K102" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="M102" s="12"/>
     </row>
@@ -12391,16 +12402,16 @@
       <c r="B103" s="14"/>
       <c r="C103" s="27"/>
       <c r="D103" s="12" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="I103" s="12" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="K103" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="M103" s="12"/>
     </row>
@@ -12411,14 +12422,14 @@
       <c r="B104" s="14"/>
       <c r="C104" s="27"/>
       <c r="D104" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I104" s="12" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="J104" s="30"/>
       <c r="K104" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.3">
@@ -12428,14 +12439,14 @@
       <c r="B105" s="14"/>
       <c r="C105" s="27"/>
       <c r="D105" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I105" s="12" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="J105" s="30"/>
       <c r="K105" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.3">
@@ -12445,14 +12456,14 @@
       <c r="B106" s="14"/>
       <c r="C106" s="27"/>
       <c r="D106" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I106" s="12" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
       <c r="J106" s="30"/>
       <c r="K106" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.3">
@@ -12462,14 +12473,14 @@
       <c r="B107" s="14"/>
       <c r="C107" s="27"/>
       <c r="D107" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I107" s="12" t="s">
-        <v>1292</v>
+        <v>1287</v>
       </c>
       <c r="J107" s="30"/>
       <c r="K107" s="36" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="108" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
@@ -12479,16 +12490,16 @@
       <c r="B108" s="14"/>
       <c r="C108" s="27"/>
       <c r="D108" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I108" s="12" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="J108" s="30" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="K108" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.3">
@@ -12498,14 +12509,14 @@
       <c r="B109" s="14"/>
       <c r="C109" s="27"/>
       <c r="D109" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I109" s="12" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="J109" s="30"/>
       <c r="K109" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.3">
@@ -12515,14 +12526,14 @@
       <c r="B110" s="14"/>
       <c r="C110" s="27"/>
       <c r="D110" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I110" s="12" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
       <c r="J110" s="30"/>
       <c r="K110" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="111" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -12532,16 +12543,16 @@
       <c r="B111" s="14"/>
       <c r="C111" s="27"/>
       <c r="D111" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I111" s="12" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="J111" s="30" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="K111" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.3">
@@ -12551,14 +12562,14 @@
       <c r="B112" s="14"/>
       <c r="C112" s="27"/>
       <c r="D112" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I112" s="12"/>
       <c r="J112" s="30" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="K112" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
@@ -12568,14 +12579,14 @@
       <c r="B113" s="14"/>
       <c r="C113" s="27"/>
       <c r="D113" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I113" s="12"/>
       <c r="J113" s="30" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="K113" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -12585,16 +12596,16 @@
       <c r="B114" s="14"/>
       <c r="C114" s="27"/>
       <c r="D114" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I114" s="12" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="J114" s="30" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="K114" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.3">
@@ -12604,16 +12615,16 @@
       <c r="B115" s="14"/>
       <c r="C115" s="27"/>
       <c r="D115" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I115" s="12" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="J115" s="30" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="K115" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
@@ -12623,16 +12634,16 @@
       <c r="B116" s="14"/>
       <c r="C116" s="27"/>
       <c r="D116" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I116" s="12" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="J116" s="30" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="K116" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="158.4" x14ac:dyDescent="0.3">
@@ -12640,16 +12651,16 @@
         <v>318</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K117" s="30" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="158.4" x14ac:dyDescent="0.3">
@@ -12657,20 +12668,20 @@
         <v>323</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E118" s="30"/>
       <c r="F118" s="30"/>
       <c r="G118" s="30"/>
       <c r="H118" s="30"/>
       <c r="I118" s="1" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="J118" s="30" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="K118" s="30" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -12678,16 +12689,16 @@
         <v>326</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="J119" s="30" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K119" s="30" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -12695,20 +12706,20 @@
         <v>331</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E120" s="31"/>
       <c r="F120" s="31"/>
       <c r="G120" s="31"/>
       <c r="H120" s="31"/>
       <c r="I120" s="1" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
       <c r="J120" s="30" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="K120" s="30" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -12716,20 +12727,20 @@
         <v>335</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E121" s="30"/>
       <c r="F121" s="30"/>
       <c r="G121" s="30"/>
       <c r="H121" s="30"/>
       <c r="I121" s="1" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="J121" s="30" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="K121" s="30" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -12737,20 +12748,20 @@
         <v>340</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E122" s="30"/>
       <c r="F122" s="30"/>
       <c r="G122" s="30"/>
       <c r="H122" s="30"/>
       <c r="I122" s="1" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="J122" s="30" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="K122" s="30" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.3">
@@ -12758,20 +12769,20 @@
         <v>345</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E123" s="30"/>
       <c r="F123" s="30"/>
       <c r="G123" s="30"/>
       <c r="H123" s="30"/>
       <c r="I123" s="1" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="J123" s="30" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="K123" s="30" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.3">
@@ -12779,20 +12790,20 @@
         <v>350</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E124" s="30"/>
       <c r="F124" s="30"/>
       <c r="G124" s="30"/>
       <c r="H124" s="30"/>
       <c r="I124" s="1" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="J124" s="30" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="K124" s="30" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.3">
@@ -12800,18 +12811,18 @@
         <v>350</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E125" s="30"/>
       <c r="F125" s="30"/>
       <c r="G125" s="30"/>
       <c r="H125" s="30"/>
       <c r="I125" s="1" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="J125" s="30"/>
       <c r="K125" s="30" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -12819,20 +12830,20 @@
         <v>354</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E126" s="32"/>
       <c r="F126" s="32"/>
       <c r="G126" s="32"/>
       <c r="H126" s="32"/>
       <c r="I126" s="1" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J126" s="30" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="K126" s="46" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -12840,20 +12851,20 @@
         <v>359</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E127" s="30"/>
       <c r="F127" s="30"/>
       <c r="G127" s="30"/>
       <c r="H127" s="30"/>
       <c r="I127" s="1" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J127" s="30" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="K127" s="30" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -12861,20 +12872,20 @@
         <v>361</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E128" s="30"/>
       <c r="F128" s="30"/>
       <c r="G128" s="30"/>
       <c r="H128" s="30"/>
       <c r="I128" s="1" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J128" s="30" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="K128" s="30" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -12882,20 +12893,20 @@
         <v>363</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E129" s="30"/>
       <c r="F129" s="30"/>
       <c r="G129" s="30"/>
       <c r="H129" s="30"/>
       <c r="I129" s="1" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J129" s="30" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="K129" s="46" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.3">
@@ -12903,20 +12914,20 @@
         <v>365</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E130" s="30"/>
       <c r="F130" s="30"/>
       <c r="G130" s="30"/>
       <c r="H130" s="30"/>
       <c r="I130" s="1" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="J130" s="30" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="K130" s="46" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.3">
@@ -12924,18 +12935,18 @@
         <v>365</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E131" s="30"/>
       <c r="F131" s="30"/>
       <c r="G131" s="30"/>
       <c r="H131" s="30"/>
       <c r="I131" s="1" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="J131" s="30"/>
       <c r="K131" s="30" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -12943,20 +12954,20 @@
         <v>370</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E132" s="30"/>
       <c r="F132" s="30"/>
       <c r="G132" s="30"/>
       <c r="H132" s="30"/>
       <c r="I132" s="1" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="J132" s="30" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="K132" s="30" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.3">
@@ -12964,18 +12975,18 @@
         <v>370</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E133" s="30"/>
       <c r="F133" s="30"/>
       <c r="G133" s="30"/>
       <c r="H133" s="30"/>
       <c r="I133" s="1" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="J133" s="30"/>
       <c r="K133" s="30" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
@@ -12983,20 +12994,20 @@
         <v>374</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E134" s="30"/>
       <c r="F134" s="30"/>
       <c r="G134" s="30"/>
       <c r="H134" s="30"/>
       <c r="I134" s="1" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="J134" s="30" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="K134" s="30" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.3">
@@ -13004,18 +13015,18 @@
         <v>374</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E135" s="30"/>
       <c r="F135" s="30"/>
       <c r="G135" s="30"/>
       <c r="H135" s="30"/>
       <c r="I135" s="1" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="J135" s="30"/>
       <c r="K135" s="30" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.3">
@@ -13023,18 +13034,18 @@
         <v>379</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E136" s="30"/>
       <c r="F136" s="30"/>
       <c r="G136" s="30"/>
       <c r="H136" s="30"/>
       <c r="I136" s="1" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="J136" s="30"/>
       <c r="K136" s="30" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.3">
@@ -13042,18 +13053,18 @@
         <v>379</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E137" s="30"/>
       <c r="F137" s="30"/>
       <c r="G137" s="30"/>
       <c r="H137" s="30"/>
       <c r="I137" s="1" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="J137" s="30"/>
       <c r="K137" s="30" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
@@ -13063,16 +13074,16 @@
       <c r="B138" s="12"/>
       <c r="C138" s="42"/>
       <c r="D138" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I138" s="12" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="K138" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.3">
@@ -13082,13 +13093,13 @@
       <c r="B139" s="12"/>
       <c r="C139" s="42"/>
       <c r="D139" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I139" s="12" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
       <c r="K139" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="72" x14ac:dyDescent="0.3">
@@ -13096,20 +13107,20 @@
         <v>387</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E140" s="30"/>
       <c r="F140" s="30"/>
       <c r="G140" s="30"/>
       <c r="H140" s="30"/>
       <c r="I140" s="1" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="J140" s="30" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="K140" s="30" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -13120,20 +13131,20 @@
         <v>185</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E141" s="30"/>
       <c r="F141" s="30"/>
       <c r="G141" s="30"/>
       <c r="H141" s="30"/>
       <c r="I141" s="1" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="J141" s="30" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="K141" s="30" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -13144,20 +13155,20 @@
         <v>189</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E142" s="30"/>
       <c r="F142" s="30"/>
       <c r="G142" s="30"/>
       <c r="H142" s="30"/>
       <c r="I142" s="1" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="J142" s="30" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="K142" s="30" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.3">
@@ -13165,18 +13176,18 @@
         <v>399</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E143" s="30"/>
       <c r="F143" s="30"/>
       <c r="G143" s="30"/>
       <c r="H143" s="30"/>
       <c r="I143" s="1" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="J143" s="30"/>
       <c r="K143" s="30" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.3">
@@ -13184,18 +13195,18 @@
         <v>399</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E144" s="30"/>
       <c r="F144" s="30"/>
       <c r="G144" s="30"/>
       <c r="H144" s="30"/>
       <c r="I144" s="1" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="J144" s="30"/>
       <c r="K144" s="30" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -13203,16 +13214,16 @@
         <v>403</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="K145" s="30" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -13220,20 +13231,20 @@
         <v>405</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E146" s="30"/>
       <c r="F146" s="30"/>
       <c r="G146" s="30"/>
       <c r="H146" s="30"/>
       <c r="I146" s="1" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J146" s="30" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="K146" s="30" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -13241,20 +13252,20 @@
         <v>407</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E147" s="30"/>
       <c r="F147" s="30"/>
       <c r="G147" s="30"/>
       <c r="H147" s="30"/>
       <c r="I147" s="1" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J147" s="30" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="K147" s="30" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -13262,20 +13273,20 @@
         <v>409</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E148" s="30"/>
       <c r="F148" s="30"/>
       <c r="G148" s="30"/>
       <c r="H148" s="30"/>
       <c r="I148" s="1" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="J148" s="30" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="K148" s="30" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.3">
@@ -13283,20 +13294,20 @@
         <v>411</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E149" s="30"/>
       <c r="F149" s="30"/>
       <c r="G149" s="30"/>
       <c r="H149" s="30"/>
       <c r="I149" s="1" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="J149" s="30" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="K149" s="30" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.3">
@@ -13304,18 +13315,18 @@
         <v>411</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E150" s="30"/>
       <c r="F150" s="30"/>
       <c r="G150" s="30"/>
       <c r="H150" s="30"/>
       <c r="I150" s="1" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="J150" s="30"/>
       <c r="K150" s="30" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.3">
@@ -13325,13 +13336,13 @@
       <c r="B151" s="12"/>
       <c r="C151" s="42"/>
       <c r="D151" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I151" s="12" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="K151" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.3">
@@ -13341,13 +13352,13 @@
       <c r="B152" s="12"/>
       <c r="C152" s="42"/>
       <c r="D152" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I152" s="12" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="K152" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.3">
@@ -13355,20 +13366,20 @@
         <v>418</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E153" s="30"/>
       <c r="F153" s="30"/>
       <c r="G153" s="30"/>
       <c r="H153" s="30"/>
       <c r="I153" s="1" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="J153" s="30" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="K153" s="30" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.3">
@@ -13376,18 +13387,18 @@
         <v>418</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E154" s="30"/>
       <c r="F154" s="30"/>
       <c r="G154" s="30"/>
       <c r="H154" s="30"/>
       <c r="I154" s="1" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="J154" s="30"/>
       <c r="K154" s="30" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.3">
@@ -13395,18 +13406,18 @@
         <v>423</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E155" s="30"/>
       <c r="F155" s="30"/>
       <c r="G155" s="30"/>
       <c r="H155" s="30"/>
       <c r="I155" s="1" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="J155" s="30"/>
       <c r="K155" s="30" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.3">
@@ -13414,18 +13425,18 @@
         <v>423</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E156" s="30"/>
       <c r="F156" s="30"/>
       <c r="G156" s="30"/>
       <c r="H156" s="30"/>
       <c r="I156" s="1" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="J156" s="30"/>
       <c r="K156" s="30" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.3">
@@ -13435,13 +13446,13 @@
       <c r="B157" s="12"/>
       <c r="C157" s="42"/>
       <c r="D157" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I157" s="12" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="K157" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.3">
@@ -13451,13 +13462,13 @@
       <c r="B158" s="12"/>
       <c r="C158" s="42"/>
       <c r="D158" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I158" s="12" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="K158" s="36" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.3">
@@ -13465,18 +13476,18 @@
         <v>430</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E159" s="30"/>
       <c r="F159" s="30"/>
       <c r="G159" s="30"/>
       <c r="H159" s="30"/>
       <c r="I159" s="1" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="J159" s="30"/>
       <c r="K159" s="30" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.3">
@@ -13486,13 +13497,13 @@
       <c r="B160" s="12"/>
       <c r="C160" s="42"/>
       <c r="D160" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I160" s="12" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="K160" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.3">
@@ -13500,18 +13511,18 @@
         <v>435</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E161" s="30"/>
       <c r="F161" s="30"/>
       <c r="G161" s="30"/>
       <c r="H161" s="30"/>
       <c r="I161" s="1" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="J161" s="30"/>
       <c r="K161" s="30" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.3">
@@ -13519,18 +13530,18 @@
         <v>440</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E162" s="30"/>
       <c r="F162" s="30"/>
       <c r="G162" s="30"/>
       <c r="H162" s="30"/>
       <c r="I162" s="1" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="J162" s="30"/>
       <c r="K162" s="30" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.3">
@@ -13540,13 +13551,13 @@
       <c r="B163" s="12"/>
       <c r="C163" s="42"/>
       <c r="D163" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I163" s="12" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="K163" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
@@ -13556,16 +13567,16 @@
       <c r="B164" s="12"/>
       <c r="C164" s="42"/>
       <c r="D164" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K164" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.3">
@@ -13575,16 +13586,16 @@
       <c r="B165"/>
       <c r="C165" s="42"/>
       <c r="D165" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="K165" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.3">
@@ -13594,16 +13605,16 @@
       <c r="B166"/>
       <c r="C166" s="42"/>
       <c r="D166" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="K166" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="167" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13612,17 +13623,17 @@
       </c>
       <c r="C167" s="1"/>
       <c r="D167" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H167"/>
       <c r="I167" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J167" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13631,17 +13642,17 @@
       </c>
       <c r="C168" s="1"/>
       <c r="D168" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H168"/>
       <c r="I168" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J168" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K168" s="1" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="169" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13650,17 +13661,17 @@
       </c>
       <c r="C169" s="1"/>
       <c r="D169" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H169"/>
       <c r="I169" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J169" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K169" s="50" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13669,17 +13680,17 @@
       </c>
       <c r="C170" s="1"/>
       <c r="D170" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H170"/>
       <c r="I170" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J170" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K170" s="1" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="171" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13688,17 +13699,17 @@
       </c>
       <c r="C171" s="1"/>
       <c r="D171" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H171"/>
       <c r="I171" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J171" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K171" s="1" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="172" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13707,17 +13718,17 @@
       </c>
       <c r="C172" s="1"/>
       <c r="D172" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H172"/>
       <c r="I172" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J172" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K172" s="1" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="173" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13726,17 +13737,17 @@
       </c>
       <c r="C173" s="1"/>
       <c r="D173" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H173"/>
       <c r="I173" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J173" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K173" s="1" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="174" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13745,17 +13756,17 @@
       </c>
       <c r="C174" s="1"/>
       <c r="D174" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H174"/>
       <c r="I174" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J174" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K174" s="1" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="175" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13764,17 +13775,17 @@
       </c>
       <c r="C175" s="1"/>
       <c r="D175" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H175"/>
       <c r="I175" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J175" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="176" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13783,17 +13794,17 @@
       </c>
       <c r="C176" s="1"/>
       <c r="D176" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H176"/>
       <c r="I176" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J176" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K176" s="1" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="177" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13802,17 +13813,17 @@
       </c>
       <c r="C177" s="1"/>
       <c r="D177" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H177"/>
       <c r="I177" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J177" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K177" s="1" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="178" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13821,17 +13832,17 @@
       </c>
       <c r="C178" s="1"/>
       <c r="D178" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H178"/>
       <c r="I178" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J178" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K178" s="1" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="179" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13840,17 +13851,17 @@
       </c>
       <c r="C179" s="1"/>
       <c r="D179" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H179"/>
       <c r="I179" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J179" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K179" s="1" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="180" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13859,17 +13870,17 @@
       </c>
       <c r="C180" s="1"/>
       <c r="D180" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H180"/>
       <c r="I180" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J180" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K180" s="1" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="181" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13878,17 +13889,17 @@
       </c>
       <c r="C181" s="1"/>
       <c r="D181" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H181"/>
       <c r="I181" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J181" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K181" s="1" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="182" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13897,17 +13908,17 @@
       </c>
       <c r="C182" s="1"/>
       <c r="D182" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H182"/>
       <c r="I182" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J182" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="183" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13916,17 +13927,17 @@
       </c>
       <c r="C183" s="1"/>
       <c r="D183" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H183"/>
       <c r="I183" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J183" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K183" s="1" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="184" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13935,17 +13946,17 @@
       </c>
       <c r="C184" s="1"/>
       <c r="D184" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H184"/>
       <c r="I184" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J184" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K184" s="1" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="185" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13954,17 +13965,17 @@
       </c>
       <c r="C185" s="1"/>
       <c r="D185" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H185"/>
       <c r="I185" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J185" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K185" s="1" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="186" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13973,17 +13984,17 @@
       </c>
       <c r="C186" s="1"/>
       <c r="D186" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H186"/>
       <c r="I186" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J186" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K186" s="1" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="187" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -13992,17 +14003,17 @@
       </c>
       <c r="C187" s="1"/>
       <c r="D187" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H187"/>
       <c r="I187" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J187" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K187" s="1" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="188" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -14011,17 +14022,17 @@
       </c>
       <c r="C188" s="1"/>
       <c r="D188" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H188"/>
       <c r="I188" s="1" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="J188" s="30" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="K188" s="1" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="189" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14031,16 +14042,16 @@
       <c r="B189" s="12"/>
       <c r="C189" s="42"/>
       <c r="D189" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I189" s="12" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="K189" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="190" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14050,16 +14061,16 @@
       <c r="B190" s="12"/>
       <c r="C190" s="42"/>
       <c r="D190" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I190" s="12" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="K190" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="191" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14069,16 +14080,16 @@
       <c r="B191" s="12"/>
       <c r="C191" s="42"/>
       <c r="D191" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I191" s="12" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="K191" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="192" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14088,16 +14099,16 @@
       <c r="B192" s="12"/>
       <c r="C192" s="42"/>
       <c r="D192" s="52" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="I192" s="12" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="J192" s="1" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="K192" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="193" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14107,16 +14118,16 @@
       <c r="B193" s="12"/>
       <c r="C193" s="42"/>
       <c r="D193" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I193" s="12" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="J193" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="K193" t="s">
         <v>1208</v>
-      </c>
-      <c r="K193" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="194" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14126,16 +14137,16 @@
       <c r="B194" s="12"/>
       <c r="C194" s="42"/>
       <c r="D194" s="52" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="I194" s="12" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="K194" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.3">
@@ -14145,14 +14156,14 @@
       <c r="B195" s="14"/>
       <c r="C195" s="27"/>
       <c r="D195" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I195" s="12" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="J195" s="30"/>
       <c r="K195" s="36" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="196" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14162,16 +14173,16 @@
       <c r="B196" s="14"/>
       <c r="C196" s="27"/>
       <c r="D196" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I196" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J196" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K196" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.3">
@@ -14180,14 +14191,14 @@
       </c>
       <c r="C197" s="1"/>
       <c r="D197" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I197" s="12" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="J197" s="30"/>
       <c r="K197" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="198" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14196,16 +14207,16 @@
       </c>
       <c r="C198" s="1"/>
       <c r="D198" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I198" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J198" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K198" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.3">
@@ -14214,14 +14225,14 @@
       </c>
       <c r="C199" s="1"/>
       <c r="D199" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I199" s="12" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="J199" s="30"/>
       <c r="K199" s="36" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="200" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14230,16 +14241,16 @@
       </c>
       <c r="C200" s="1"/>
       <c r="D200" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I200" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J200" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K200" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.3">
@@ -14248,14 +14259,14 @@
       </c>
       <c r="C201" s="1"/>
       <c r="D201" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I201" s="12" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="J201" s="30"/>
       <c r="K201" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="202" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14264,16 +14275,16 @@
       </c>
       <c r="C202" s="1"/>
       <c r="D202" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I202" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J202" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K202" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.3">
@@ -14282,14 +14293,14 @@
       </c>
       <c r="C203" s="1"/>
       <c r="D203" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I203" s="12" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="J203" s="30"/>
       <c r="K203" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="204" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14298,16 +14309,16 @@
       </c>
       <c r="C204" s="1"/>
       <c r="D204" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I204" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J204" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K204" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.3">
@@ -14316,14 +14327,14 @@
       </c>
       <c r="C205" s="1"/>
       <c r="D205" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I205" s="12" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="J205" s="30"/>
       <c r="K205" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="206" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14332,16 +14343,16 @@
       </c>
       <c r="C206" s="1"/>
       <c r="D206" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I206" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J206" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K206" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.3">
@@ -14350,14 +14361,14 @@
       </c>
       <c r="C207" s="1"/>
       <c r="D207" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="J207" s="30"/>
       <c r="K207" s="36" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="208" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14366,16 +14377,16 @@
       </c>
       <c r="C208" s="1"/>
       <c r="D208" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J208" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K208" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.3">
@@ -14384,14 +14395,14 @@
       </c>
       <c r="C209" s="1"/>
       <c r="D209" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="J209" s="30"/>
       <c r="K209" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="210" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14400,16 +14411,16 @@
       </c>
       <c r="C210" s="1"/>
       <c r="D210" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J210" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K210" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.3">
@@ -14418,14 +14429,14 @@
       </c>
       <c r="C211" s="1"/>
       <c r="D211" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I211" s="12" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="J211" s="30"/>
       <c r="K211" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="212" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14434,16 +14445,16 @@
       </c>
       <c r="C212" s="1"/>
       <c r="D212" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I212" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J212" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K212" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.3">
@@ -14452,14 +14463,14 @@
       </c>
       <c r="C213" s="1"/>
       <c r="D213" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I213" s="12" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="J213" s="30"/>
       <c r="K213" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="214" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14468,16 +14479,16 @@
       </c>
       <c r="C214" s="1"/>
       <c r="D214" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I214" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J214" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K214" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.3">
@@ -14486,14 +14497,14 @@
       </c>
       <c r="C215" s="1"/>
       <c r="D215" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I215" s="12" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="J215" s="30"/>
       <c r="K215" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="216" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14502,16 +14513,16 @@
       </c>
       <c r="C216"/>
       <c r="D216" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I216" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J216" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K216" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.3">
@@ -14520,14 +14531,14 @@
       </c>
       <c r="C217" s="1"/>
       <c r="D217" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I217" s="12" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="J217" s="30"/>
       <c r="K217" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="218" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14536,16 +14547,16 @@
       </c>
       <c r="C218" s="1"/>
       <c r="D218" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I218" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J218" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K218" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.3">
@@ -14554,14 +14565,14 @@
       </c>
       <c r="C219" s="1"/>
       <c r="D219" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I219" s="12" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="J219" s="30"/>
       <c r="K219" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="220" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14570,16 +14581,16 @@
       </c>
       <c r="C220" s="1"/>
       <c r="D220" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I220" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J220" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K220" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.3">
@@ -14588,14 +14599,14 @@
       </c>
       <c r="C221" s="1"/>
       <c r="D221" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I221" s="12" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="J221" s="30"/>
       <c r="K221" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="222" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14604,16 +14615,16 @@
       </c>
       <c r="C222" s="1"/>
       <c r="D222" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I222" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J222" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K222" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.3">
@@ -14622,14 +14633,14 @@
       </c>
       <c r="C223" s="1"/>
       <c r="D223" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I223" s="12" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="J223" s="30"/>
       <c r="K223" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="224" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14638,16 +14649,16 @@
       </c>
       <c r="C224" s="1"/>
       <c r="D224" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I224" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J224" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K224" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.3">
@@ -14656,14 +14667,14 @@
       </c>
       <c r="C225" s="1"/>
       <c r="D225" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I225" s="12" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="J225" s="30"/>
       <c r="K225" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="226" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14672,16 +14683,16 @@
       </c>
       <c r="C226" s="1"/>
       <c r="D226" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I226" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J226" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K226" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.3">
@@ -14690,14 +14701,14 @@
       </c>
       <c r="C227" s="1"/>
       <c r="D227" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I227" s="12" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="J227" s="30"/>
       <c r="K227" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="228" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14706,16 +14717,16 @@
       </c>
       <c r="C228" s="1"/>
       <c r="D228" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I228" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J228" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K228" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.3">
@@ -14724,14 +14735,14 @@
       </c>
       <c r="C229" s="1"/>
       <c r="D229" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I229" s="12" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="J229" s="30"/>
       <c r="K229" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="230" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14740,16 +14751,16 @@
       </c>
       <c r="C230" s="1"/>
       <c r="D230" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I230" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J230" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K230" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.3">
@@ -14758,14 +14769,14 @@
       </c>
       <c r="C231" s="1"/>
       <c r="D231" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I231" s="12" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="J231" s="30"/>
       <c r="K231" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="232" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14774,16 +14785,16 @@
       </c>
       <c r="C232" s="1"/>
       <c r="D232" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I232" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J232" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K232" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.3">
@@ -14792,14 +14803,14 @@
       </c>
       <c r="C233" s="1"/>
       <c r="D233" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I233" s="12" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="J233" s="30"/>
       <c r="K233" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="234" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14808,16 +14819,16 @@
       </c>
       <c r="C234" s="1"/>
       <c r="D234" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I234" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J234" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K234" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.3">
@@ -14826,14 +14837,14 @@
       </c>
       <c r="C235" s="1"/>
       <c r="D235" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I235" s="12" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="J235" s="30"/>
       <c r="K235" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="236" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14842,16 +14853,16 @@
       </c>
       <c r="C236" s="1"/>
       <c r="D236" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I236" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J236" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K236" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.3">
@@ -14860,14 +14871,14 @@
       </c>
       <c r="C237" s="1"/>
       <c r="D237" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I237" s="12" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="J237" s="30"/>
       <c r="K237" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="238" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14876,16 +14887,16 @@
       </c>
       <c r="C238" s="1"/>
       <c r="D238" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I238" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J238" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K238" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.3">
@@ -14894,14 +14905,14 @@
       </c>
       <c r="C239" s="1"/>
       <c r="D239" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I239" s="12" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="J239" s="30"/>
       <c r="K239" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="240" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14910,16 +14921,16 @@
       </c>
       <c r="C240" s="1"/>
       <c r="D240" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I240" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J240" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K240" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.3">
@@ -14929,14 +14940,14 @@
       <c r="B241" s="14"/>
       <c r="C241" s="27"/>
       <c r="D241" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I241" s="12" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="J241" s="30"/>
       <c r="K241" s="36" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="242" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14945,16 +14956,16 @@
       </c>
       <c r="C242" s="1"/>
       <c r="D242" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I242" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J242" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K242" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.3">
@@ -14964,14 +14975,14 @@
       <c r="B243" s="14"/>
       <c r="C243" s="27"/>
       <c r="D243" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I243" s="12" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="J243" s="30"/>
       <c r="K243" s="36" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="244" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -14980,16 +14991,16 @@
       </c>
       <c r="C244" s="1"/>
       <c r="D244" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I244" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J244" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K244" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.3">
@@ -14999,14 +15010,14 @@
       <c r="B245" s="14"/>
       <c r="C245" s="27"/>
       <c r="D245" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I245" s="12" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="J245" s="30"/>
       <c r="K245" s="36" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="246" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -15015,16 +15026,16 @@
       </c>
       <c r="C246" s="1"/>
       <c r="D246" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I246" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J246" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K246" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.3">
@@ -15033,14 +15044,14 @@
       </c>
       <c r="C247" s="1"/>
       <c r="D247" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I247" s="12" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="J247" s="30"/>
       <c r="K247" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="248" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -15049,16 +15060,16 @@
       </c>
       <c r="C248" s="1"/>
       <c r="D248" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I248" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J248" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K248" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.3">
@@ -15067,14 +15078,14 @@
       </c>
       <c r="C249" s="1"/>
       <c r="D249" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I249" s="12" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="J249" s="30"/>
       <c r="K249" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="250" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -15083,16 +15094,16 @@
       </c>
       <c r="C250" s="1"/>
       <c r="D250" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I250" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J250" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K250" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.3">
@@ -15101,14 +15112,14 @@
       </c>
       <c r="C251" s="1"/>
       <c r="D251" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I251" s="12" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="J251" s="30"/>
       <c r="K251" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="252" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -15117,16 +15128,16 @@
       </c>
       <c r="C252" s="1"/>
       <c r="D252" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I252" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J252" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K252" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.3">
@@ -15135,14 +15146,14 @@
       </c>
       <c r="C253" s="1"/>
       <c r="D253" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I253" s="12" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="J253" s="30"/>
       <c r="K253" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="254" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -15151,183 +15162,183 @@
       </c>
       <c r="C254" s="1"/>
       <c r="D254" s="12" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="I254" s="12" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="J254" s="30" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K254" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A255" s="14" t="s">
         <v>626</v>
       </c>
       <c r="C255" s="1"/>
       <c r="D255" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I255" s="12" t="s">
-        <v>1263</v>
+        <v>1330</v>
       </c>
       <c r="J255" s="30" t="s">
-        <v>1103</v>
+        <v>1333</v>
       </c>
       <c r="K255" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A256" s="14" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C256" s="1"/>
       <c r="D256" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I256" s="12" t="s">
-        <v>1263</v>
+        <v>1330</v>
       </c>
       <c r="J256" s="30" t="s">
-        <v>1103</v>
+        <v>1333</v>
       </c>
       <c r="K256" t="s">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A257" s="14" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C257" s="1"/>
       <c r="D257" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I257" s="12" t="s">
-        <v>1263</v>
+        <v>1331</v>
       </c>
       <c r="J257" s="30" t="s">
-        <v>1103</v>
+        <v>1334</v>
       </c>
       <c r="K257" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A258" s="14" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C258" s="1"/>
       <c r="D258" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I258" s="12" t="s">
-        <v>1264</v>
+        <v>1332</v>
       </c>
       <c r="J258" s="30" t="s">
-        <v>1103</v>
+        <v>1334</v>
       </c>
       <c r="K258" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" s="14" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B259" s="14"/>
       <c r="C259" s="27"/>
       <c r="D259" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I259" s="12" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="J259" s="30" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="K259" s="30" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260" s="14" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B260" s="14"/>
       <c r="C260" s="27"/>
       <c r="D260" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I260" s="12" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="J260" s="30" t="s">
+        <v>1092</v>
+      </c>
+      <c r="K260" s="30" t="s">
         <v>1094</v>
-      </c>
-      <c r="K260" s="30" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261" s="14" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B261" s="14"/>
       <c r="C261" s="27"/>
       <c r="D261" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I261" s="12" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
       <c r="J261" s="30" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="K261" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262" s="14" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B262" s="14"/>
       <c r="C262" s="27"/>
       <c r="D262" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I262" s="12" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="J262" s="30" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="K262" s="30" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263" s="14" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B263" s="14"/>
       <c r="C263" s="27"/>
       <c r="D263" s="12" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="I263" s="12" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="J263" s="30" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="K263" s="30" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.3">
@@ -17727,7 +17738,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -17739,7 +17750,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -17750,10 +17761,10 @@
         <v>23</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D8" s="35" t="s">
         <v>10</v>
@@ -17764,13 +17775,13 @@
         <v>254</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="D9" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -17778,13 +17789,13 @@
         <v>258</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="D10" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -17792,13 +17803,13 @@
         <v>263</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="D11" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -17806,13 +17817,13 @@
         <v>268</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="D12" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -17820,13 +17831,13 @@
         <v>273</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="D13" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -17834,13 +17845,13 @@
         <v>283</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="D14" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -17848,13 +17859,13 @@
         <v>288</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="D15" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -17862,13 +17873,13 @@
         <v>296</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>1267</v>
+        <v>1262</v>
       </c>
       <c r="D16" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -17876,13 +17887,13 @@
         <v>307</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -17890,13 +17901,13 @@
         <v>312</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -17904,13 +17915,13 @@
         <v>316</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -17918,13 +17929,13 @@
         <v>318</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -17932,13 +17943,13 @@
         <v>323</v>
       </c>
       <c r="B21" s="47" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -17946,13 +17957,13 @@
         <v>326</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="D22" s="41" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="23" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -17960,13 +17971,13 @@
         <v>331</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="D23" s="41" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="24" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -17974,13 +17985,13 @@
         <v>335</v>
       </c>
       <c r="B24" s="47" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="D24" s="41" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="25" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -17988,13 +17999,13 @@
         <v>340</v>
       </c>
       <c r="B25" s="47" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>1270</v>
+        <v>1265</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="26" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18002,13 +18013,13 @@
         <v>345</v>
       </c>
       <c r="B26" s="47" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="27" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18016,13 +18027,13 @@
         <v>350</v>
       </c>
       <c r="B27" s="47" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18030,13 +18041,13 @@
         <v>354</v>
       </c>
       <c r="B28" s="47" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C28" s="41" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18044,13 +18055,13 @@
         <v>359</v>
       </c>
       <c r="B29" s="47" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="D29" s="41" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="30" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18058,13 +18069,13 @@
         <v>361</v>
       </c>
       <c r="B30" s="41" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="D30" s="41" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="31" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18072,13 +18083,13 @@
         <v>363</v>
       </c>
       <c r="B31" s="41" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="32" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18086,13 +18097,13 @@
         <v>365</v>
       </c>
       <c r="B32" s="41" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="33" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18100,13 +18111,13 @@
         <v>370</v>
       </c>
       <c r="B33" s="41" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18114,13 +18125,13 @@
         <v>374</v>
       </c>
       <c r="B34" s="41" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="35" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18128,13 +18139,13 @@
         <v>379</v>
       </c>
       <c r="B35" s="41" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18142,13 +18153,13 @@
         <v>383</v>
       </c>
       <c r="B36" s="41" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="37" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18156,13 +18167,13 @@
         <v>387</v>
       </c>
       <c r="B37" s="41" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C37" s="41" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18170,13 +18181,13 @@
         <v>392</v>
       </c>
       <c r="B38" s="41" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18184,13 +18195,13 @@
         <v>399</v>
       </c>
       <c r="B39" s="41" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="40" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18198,13 +18209,13 @@
         <v>403</v>
       </c>
       <c r="B40" s="41" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C40" s="41" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="41" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18212,13 +18223,13 @@
         <v>405</v>
       </c>
       <c r="B41" s="41" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C41" s="41" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="D41" s="41" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18226,13 +18237,13 @@
         <v>407</v>
       </c>
       <c r="B42" s="41" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C42" s="41" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="D42" s="41" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="43" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18240,13 +18251,13 @@
         <v>409</v>
       </c>
       <c r="B43" s="41" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="D43" s="41" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="44" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18254,13 +18265,13 @@
         <v>411</v>
       </c>
       <c r="B44" s="41" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C44" s="41" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="D44" s="41" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="45" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18268,13 +18279,13 @@
         <v>413</v>
       </c>
       <c r="B45" s="41" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C45" s="41" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
       <c r="D45" s="41" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="46" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18282,13 +18293,13 @@
         <v>418</v>
       </c>
       <c r="B46" s="41" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="D46" s="41" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="47" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18296,13 +18307,13 @@
         <v>423</v>
       </c>
       <c r="B47" s="41" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C47" s="41" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
       <c r="D47" s="41" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="48" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18310,13 +18321,13 @@
         <v>425</v>
       </c>
       <c r="B48" s="41" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C48" s="41" t="s">
-        <v>1280</v>
+        <v>1275</v>
       </c>
       <c r="D48" s="41" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="49" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18324,13 +18335,13 @@
         <v>430</v>
       </c>
       <c r="B49" s="41" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C49" s="41" t="s">
-        <v>1281</v>
+        <v>1276</v>
       </c>
       <c r="D49" s="41" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="50" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18338,13 +18349,13 @@
         <v>435</v>
       </c>
       <c r="B50" s="41" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C50" s="41" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="D50" s="41" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="51" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18352,13 +18363,13 @@
         <v>440</v>
       </c>
       <c r="B51" s="41" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C51" s="41" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="D51" s="41" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -18366,13 +18377,13 @@
         <v>524</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C52" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -18380,13 +18391,13 @@
         <v>528</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C53" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="D53" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="54" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -18463,7 +18474,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -18471,7 +18482,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -18482,10 +18493,10 @@
         <v>23</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D8" s="35" t="s">
         <v>10</v>
@@ -18496,13 +18507,13 @@
         <v>248</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C9" s="41" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D9" s="41" t="s">
         <v>1083</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18510,13 +18521,13 @@
         <v>278</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="11" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18524,13 +18535,13 @@
         <v>335</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18538,13 +18549,13 @@
         <v>345</v>
       </c>
       <c r="B12" s="41" t="s">
+        <v>729</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>730</v>
+      </c>
+      <c r="D12" s="41" t="s">
         <v>731</v>
-      </c>
-      <c r="C12" s="41" t="s">
-        <v>732</v>
-      </c>
-      <c r="D12" s="41" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18552,13 +18563,13 @@
         <v>392</v>
       </c>
       <c r="B13" s="41" t="s">
+        <v>732</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>733</v>
+      </c>
+      <c r="D13" s="41" t="s">
         <v>734</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>735</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -18566,13 +18577,13 @@
         <v>392</v>
       </c>
       <c r="B14" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="C14" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="D14" s="41" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="15" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3">
@@ -18580,13 +18591,13 @@
         <v>519</v>
       </c>
       <c r="B15" s="41" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="41" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -18678,7 +18689,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -18689,7 +18700,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -18700,10 +18711,10 @@
         <v>27</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D8" s="35" t="s">
         <v>10</v>
@@ -18711,72 +18722,72 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>737</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D9" t="s">
         <v>739</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>740</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>1320</v>
-      </c>
-      <c r="D9" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="D10" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>742</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D11" t="s">
         <v>744</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>1322</v>
-      </c>
-      <c r="D11" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="D12" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>747</v>
+      </c>
+      <c r="B13" t="s">
+        <v>748</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D13" t="s">
         <v>749</v>
-      </c>
-      <c r="B13" t="s">
-        <v>750</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>1324</v>
-      </c>
-      <c r="D13" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -18880,7 +18891,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -18891,7 +18902,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -18902,10 +18913,10 @@
         <v>27</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D8" s="35" t="s">
         <v>10</v>
@@ -18913,226 +18924,226 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="C9" t="s">
+        <v>753</v>
+      </c>
+      <c r="D9" t="s">
         <v>754</v>
-      </c>
-      <c r="C9" t="s">
-        <v>755</v>
-      </c>
-      <c r="D9" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B10" t="s">
+        <v>755</v>
+      </c>
+      <c r="C10" t="s">
+        <v>756</v>
+      </c>
+      <c r="D10" t="s">
         <v>757</v>
-      </c>
-      <c r="C10" t="s">
-        <v>758</v>
-      </c>
-      <c r="D10" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B11" t="s">
+        <v>758</v>
+      </c>
+      <c r="C11" t="s">
+        <v>759</v>
+      </c>
+      <c r="D11" t="s">
         <v>760</v>
-      </c>
-      <c r="C11" t="s">
-        <v>761</v>
-      </c>
-      <c r="D11" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B12" t="s">
+        <v>761</v>
+      </c>
+      <c r="C12" t="s">
+        <v>762</v>
+      </c>
+      <c r="D12" t="s">
         <v>763</v>
-      </c>
-      <c r="C12" t="s">
-        <v>764</v>
-      </c>
-      <c r="D12" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B13" t="s">
+        <v>764</v>
+      </c>
+      <c r="C13" t="s">
+        <v>765</v>
+      </c>
+      <c r="D13" t="s">
         <v>766</v>
-      </c>
-      <c r="C13" t="s">
-        <v>767</v>
-      </c>
-      <c r="D13" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="D14" t="s">
         <v>769</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>770</v>
-      </c>
-      <c r="D14" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B15" t="s">
+        <v>770</v>
+      </c>
+      <c r="C15" t="s">
+        <v>771</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>772</v>
-      </c>
-      <c r="C15" t="s">
-        <v>773</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B16" t="s">
+        <v>773</v>
+      </c>
+      <c r="C16" t="s">
+        <v>774</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>775</v>
-      </c>
-      <c r="C16" t="s">
-        <v>776</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B17" t="s">
+        <v>776</v>
+      </c>
+      <c r="C17" t="s">
+        <v>777</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>778</v>
-      </c>
-      <c r="C17" t="s">
-        <v>779</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B18" t="s">
+        <v>779</v>
+      </c>
+      <c r="C18" t="s">
+        <v>780</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>781</v>
-      </c>
-      <c r="C18" t="s">
-        <v>782</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B19" t="s">
+        <v>782</v>
+      </c>
+      <c r="C19" t="s">
+        <v>783</v>
+      </c>
+      <c r="D19" t="s">
         <v>784</v>
-      </c>
-      <c r="C19" t="s">
-        <v>785</v>
-      </c>
-      <c r="D19" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>785</v>
+      </c>
+      <c r="B20" t="s">
+        <v>786</v>
+      </c>
+      <c r="C20" t="s">
         <v>787</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>788</v>
-      </c>
-      <c r="C20" t="s">
-        <v>789</v>
-      </c>
-      <c r="D20" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B21" t="s">
+        <v>789</v>
+      </c>
+      <c r="C21" t="s">
+        <v>790</v>
+      </c>
+      <c r="D21" t="s">
         <v>791</v>
-      </c>
-      <c r="C21" t="s">
-        <v>792</v>
-      </c>
-      <c r="D21" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>792</v>
+      </c>
+      <c r="B22" t="s">
+        <v>793</v>
+      </c>
+      <c r="C22" t="s">
         <v>794</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" t="s">
         <v>795</v>
-      </c>
-      <c r="C22" t="s">
-        <v>796</v>
-      </c>
-      <c r="D22" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B23" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="C23" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="D23" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B24" t="s">
+        <v>796</v>
+      </c>
+      <c r="C24" t="s">
+        <v>797</v>
+      </c>
+      <c r="D24" t="s">
         <v>798</v>
-      </c>
-      <c r="C24" t="s">
-        <v>799</v>
-      </c>
-      <c r="D24" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -19208,382 +19219,382 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B5" s="5"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B7" s="7"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="51" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="51" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="51" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="51" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="51" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="51" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B14" s="51" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="51" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="51" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="B16" s="51" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="51" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="51" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="51" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="51" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="51" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="51" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="51" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="51" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="51" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="51" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="51" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="51" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="51" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="51" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="B30" s="51" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="51" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B31" s="51" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="51" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="51" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="B33" s="51" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="B34" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="B35" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="B36" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="B37" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="B38" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="B39" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="B40" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="B41" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="51" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="B42" s="51" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="51" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="51" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="B44" s="51" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="51" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="B45" s="51" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="51" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="B46" s="51" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="51" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="B47" s="51" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="51" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B48" s="51" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="51" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="B49" s="51" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="B50" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="B51" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="B52" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="B53" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
     </row>
   </sheetData>
@@ -19632,7 +19643,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B5" s="22"/>
       <c r="C5" s="5"/>
@@ -19640,7 +19651,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -19652,13 +19663,13 @@
         <v>27</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>803</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>804</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>805</v>
       </c>
       <c r="E8" s="35" t="s">
         <v>10</v>
@@ -19666,95 +19677,95 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="E9" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="E10" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="E11" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>806</v>
+      </c>
+      <c r="C12" t="s">
+        <v>807</v>
+      </c>
+      <c r="D12" s="29" t="s">
         <v>808</v>
       </c>
-      <c r="C12" t="s">
-        <v>809</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>810</v>
-      </c>
       <c r="E12" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>809</v>
+      </c>
+      <c r="C13" t="s">
+        <v>810</v>
+      </c>
+      <c r="D13" s="29" t="s">
         <v>811</v>
       </c>
-      <c r="C13" t="s">
-        <v>812</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>813</v>
-      </c>
       <c r="E13" s="36" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C14" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
